--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486757_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486757_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. CORREA BOULATOVA</t>
+          <t>P. PEREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3922</v>
+        <v>6.9937</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4552</v>
+        <v>5.4363</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.063</v>
+        <v>1.5575</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5427</v>
+        <v>3.2395</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4003</v>
+        <v>3.2825</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1424</v>
+        <v>-0.043</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1093</v>
+        <v>3.0684</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9872</v>
+        <v>2.4557</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1221</v>
+        <v>0.6127</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4334</v>
+        <v>0.1711</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4131</v>
+        <v>0.8268</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0203</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3515</v>
+        <v>2.1239</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3515</v>
+        <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>6.9228</v>
+        <v>0.7309</v>
       </c>
       <c r="T2" t="n">
-        <v>6.3153</v>
+        <v>0.8546</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6075</v>
+        <v>-0.1236</v>
       </c>
       <c r="V2" t="n">
-        <v>-4.4248</v>
+        <v>0.8995</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.9694</v>
+        <v>1.5133</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4554</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. PEREZ FERNANDEZ</t>
+          <t>M. ESTEBANEZ ESCUDERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.136</v>
+        <v>5.184</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5537</v>
+        <v>1.9945</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5823</v>
+        <v>3.1895</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2395</v>
+        <v>3.2944</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2825</v>
+        <v>0.7173</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.043</v>
+        <v>2.5771</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0684</v>
+        <v>1.0058</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4557</v>
+        <v>-0.8683</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6127</v>
+        <v>1.8741</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1711</v>
+        <v>2.2886</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8268</v>
+        <v>1.5856</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1239</v>
+        <v>0.9654</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1239</v>
+        <v>0.9654</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1268</v>
+        <v>0.9242</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.028</v>
+        <v>0.703</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0988</v>
+        <v>0.2211</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5133</v>
+        <v>0.2856</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6138</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ESTEBANEZ ESCUDERO</t>
+          <t>I. CORREA BOULATOVA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7124</v>
+        <v>2.8964</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3739</v>
+        <v>3.456</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3385</v>
+        <v>-0.5596</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2944</v>
+        <v>2.5427</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7173</v>
+        <v>2.4003</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5771</v>
+        <v>0.1424</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0058</v>
+        <v>2.1093</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8683</v>
+        <v>1.9872</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8741</v>
+        <v>0.1221</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2886</v>
+        <v>0.4334</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5856</v>
+        <v>0.4131</v>
       </c>
       <c r="O4" t="n">
-        <v>0.703</v>
+        <v>0.0203</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4526</v>
+        <v>3.4269</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0825</v>
+        <v>3.3161</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3701</v>
+        <v>0.1108</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-4.4248</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2856</v>
+        <v>-1.9694</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GARCIA CASARRUBIOS CASTRO</t>
+          <t>M. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1021</v>
+        <v>2.7496</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5026</v>
+        <v>0.4911</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6048</v>
+        <v>2.2585</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9779</v>
+        <v>2.0974</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1452</v>
+        <v>2.545</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1673</v>
+        <v>-0.4476</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0547</v>
+        <v>0.7673</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9733000000000001</v>
+        <v>1.3731</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0814</v>
+        <v>-0.6058</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9232</v>
+        <v>1.3301</v>
       </c>
       <c r="N5" t="n">
         <v>1.1719</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2487</v>
+        <v>0.1582</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7377</v>
+        <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6882</v>
+        <v>0.5517</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7443</v>
+        <v>0.6892</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9439</v>
+        <v>-0.1375</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3709</v>
+        <v>-0.2856</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3217</v>
+        <v>2.5533</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6297</v>
+        <v>1.8366</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.7168</v>
       </c>
       <c r="G6" t="n">
         <v>2.8016</v>
@@ -922,13 +922,13 @@
         <v>1.1585</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2923</v>
+        <v>0.524</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3584</v>
+        <v>0.5652</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.066</v>
+        <v>-0.0412</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GONZALEZ NOGALES</t>
+          <t>D. GARCIA CASARRUBIOS CASTRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0901</v>
+        <v>2.2967</v>
       </c>
       <c r="E7" t="n">
-        <v>2.2605</v>
+        <v>-0.8611</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1704</v>
+        <v>3.1578</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1565</v>
+        <v>1.9779</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7103</v>
+        <v>2.1452</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-0.1673</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6747</v>
+        <v>1.0547</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0213</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6534</v>
+        <v>0.0814</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5182</v>
+        <v>0.9232</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6889999999999999</v>
+        <v>1.1719</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2072</v>
+        <v>-0.2487</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9654</v>
+        <v>1.7377</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3198</v>
+        <v>0.8827</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9374</v>
+        <v>0.3858</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6176</v>
+        <v>0.4969</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6138</v>
+        <v>-0.3709</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6138</v>
+        <v>-0.3709</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. ALONSO MENOR</t>
+          <t>J. GONZALEZ NOGALES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0852</v>
+        <v>2.1909</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8228</v>
+        <v>2.2123</v>
       </c>
       <c r="F8" t="n">
-        <v>3.908</v>
+        <v>-0.0214</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8906</v>
+        <v>1.1565</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1234</v>
+        <v>1.7103</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2328</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.2138</v>
+        <v>1.6747</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.6057</v>
+        <v>1.0213</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6081</v>
+        <v>0.6534</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3232</v>
+        <v>-0.5182</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4822</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8409</v>
+        <v>-1.2072</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9308</v>
+        <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6901</v>
+        <v>0.4206</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3643</v>
+        <v>0.8891</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3258</v>
+        <v>-0.4686</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2856</v>
+        <v>0.6138</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0426</v>
+        <v>0.6138</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5105</v>
+        <v>1.6279</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7527</v>
+        <v>0.4976</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7577</v>
+        <v>1.1302</v>
       </c>
       <c r="G9" t="n">
         <v>0.0488</v>
@@ -1156,13 +1156,13 @@
         <v>0.9654</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4962</v>
+        <v>0.6136</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9374</v>
+        <v>0.6823</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4412</v>
+        <v>-0.0687</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ALONSO MENOR</t>
+          <t>L. ALONSO MENOR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4092</v>
+        <v>0.7117</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7499</v>
+        <v>-3.2707</v>
       </c>
       <c r="F10" t="n">
-        <v>2.1591</v>
+        <v>3.9825</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0974</v>
+        <v>-1.8906</v>
       </c>
       <c r="H10" t="n">
-        <v>2.545</v>
+        <v>-2.1234</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4476</v>
+        <v>0.2328</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7673</v>
+        <v>-3.2138</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3731</v>
+        <v>-2.6057</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6058</v>
+        <v>-0.6081</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3301</v>
+        <v>1.3232</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1719</v>
+        <v>0.4822</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1582</v>
+        <v>0.8409</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3515</v>
+        <v>1.9308</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7887</v>
+        <v>2.3167</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5518</v>
+        <v>1.9164</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2369</v>
+        <v>0.4003</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2856</v>
+        <v>0.2856</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.0426</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2856</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6442</v>
+        <v>0.0757</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0204</v>
+        <v>0.6001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6237</v>
+        <v>-0.5244</v>
       </c>
       <c r="G11" t="n">
         <v>0.5173</v>
@@ -1312,13 +1312,13 @@
         <v>0.1931</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1269</v>
+        <v>0.593</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0552</v>
+        <v>0.5653</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0717</v>
+        <v>0.0277</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2277</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.6763</v>
+        <v>-0.3152</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3489</v>
+        <v>-1.2112</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6726</v>
+        <v>0.8961</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8556</v>
@@ -1390,13 +1390,13 @@
         <v>0.5792</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4579</v>
+        <v>0.9032</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3311</v>
+        <v>0.8065</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1268</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9421</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9199</v>
+        <v>-1.1697</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.3271</v>
+        <v>-1.6514</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4072</v>
+        <v>0.4817</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1003</v>
@@ -1468,13 +1468,13 @@
         <v>2.1239</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6011</v>
+        <v>1.3513</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7718</v>
+        <v>1.4476</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1707</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6138</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.519</v>
+        <v>25.795</v>
       </c>
       <c r="E14" t="n">
-        <v>9.254</v>
+        <v>9.530099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>16.2651</v>
+        <v>16.2652</v>
       </c>
       <c r="G14" t="n">
         <v>12.8296</v>
@@ -1519,7 +1519,7 @@
         <v>-1.3113</v>
       </c>
       <c r="J14" t="n">
-        <v>6.046900000000002</v>
+        <v>6.046900000000003</v>
       </c>
       <c r="K14" t="n">
         <v>6.216</v>
@@ -1546,19 +1546,19 @@
         <v>15.4463</v>
       </c>
       <c r="S14" t="n">
-        <v>12.9628</v>
+        <v>13.2388</v>
       </c>
       <c r="T14" t="n">
-        <v>12.5453</v>
+        <v>12.8211</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4176000000000003</v>
+        <v>0.4176999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.066000000000001</v>
+        <v>-6.066</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3154000000000002</v>
+        <v>0.3154000000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-6.3814</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.847</v>
+        <v>1.6115</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9306</v>
+        <v>1.9656</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.3541</v>
       </c>
       <c r="G15" t="n">
         <v>2.4307</v>
@@ -1624,13 +1624,13 @@
         <v>1.3515</v>
       </c>
       <c r="S15" t="n">
-        <v>1.953</v>
+        <v>-0.2826</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9506</v>
+        <v>0.9856</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9977</v>
+        <v>-1.2682</v>
       </c>
       <c r="V15" t="n">
         <v>0.0426</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.0522</v>
+        <v>-1.1144</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3356</v>
+        <v>1.7493</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.3878</v>
+        <v>-2.8637</v>
       </c>
       <c r="G16" t="n">
         <v>1.216</v>
@@ -1702,13 +1702,13 @@
         <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.5305</v>
+        <v>-2.5927</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7178</v>
+        <v>-0.3042</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.8126</v>
+        <v>-2.2885</v>
       </c>
       <c r="V16" t="n">
         <v>1.2277</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. BOUBACAR</t>
+          <t>A. SOUSA SILVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.1058</v>
+        <v>-2.3927</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.1268</v>
+        <v>-1.1372</v>
       </c>
       <c r="F17" t="n">
-        <v>1.021</v>
+        <v>-1.2554</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.473</v>
+        <v>-2.753</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8762</v>
+        <v>-3.4968</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5969</v>
+        <v>0.7438</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.4303</v>
+        <v>-1.5368</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.9443</v>
+        <v>-2.1157</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.486</v>
+        <v>0.5788</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0427</v>
+        <v>-1.2162</v>
       </c>
       <c r="N17" t="n">
-        <v>0.06809999999999999</v>
+        <v>-1.3811</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1108</v>
+        <v>0.165</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.1239</v>
+        <v>0.9654</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4357</v>
+        <v>-2.4892</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.028</v>
+        <v>-0.4765</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4077</v>
+        <v>-2.0127</v>
       </c>
       <c r="V17" t="n">
-        <v>1.9268</v>
+        <v>1.8842</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2277</v>
+        <v>1.8415</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SOUSA SILVA</t>
+          <t>Y. BOUBACAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.5993</v>
+        <v>-2.8011</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.068</v>
+        <v>-4.0234</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5312</v>
+        <v>1.2223</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.753</v>
+        <v>-2.473</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.4968</v>
+        <v>-1.8762</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7438</v>
+        <v>-0.5969</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5368</v>
+        <v>-2.4303</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.1157</v>
+        <v>-1.9443</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5788</v>
+        <v>-0.486</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2162</v>
+        <v>-0.0427</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3811</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>0.165</v>
+        <v>-0.1108</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9654</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9308</v>
+        <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.6958</v>
+        <v>-0.131</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4073</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.2885</v>
+        <v>-0.2064</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8842</v>
+        <v>1.9268</v>
       </c>
       <c r="W18" t="n">
-        <v>1.8415</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0426</v>
+        <v>0.6991000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.5143</v>
+        <v>-5.564</v>
       </c>
       <c r="E19" t="n">
         <v>-2.6017</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.9126</v>
+        <v>-2.9623</v>
       </c>
       <c r="G19" t="n">
         <v>-3.8443</v>
@@ -1936,13 +1936,13 @@
         <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.3498</v>
+        <v>-2.3995</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1107</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.2391</v>
+        <v>-2.2888</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2856</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.9668</v>
+        <v>-5.9297</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.4507</v>
+        <v>-5.037</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5161</v>
+        <v>-0.8927</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6738</v>
@@ -2014,13 +2014,13 @@
         <v>1.7377</v>
       </c>
       <c r="S20" t="n">
-        <v>-3.5746</v>
+        <v>-2.5375</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5523</v>
+        <v>-0.1386</v>
       </c>
       <c r="U20" t="n">
-        <v>-3.0223</v>
+        <v>-2.3989</v>
       </c>
       <c r="V20" t="n">
         <v>0.3709</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-8.127700000000001</v>
+        <v>-7.9498</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.2841</v>
+        <v>-7.1807</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8436</v>
+        <v>-0.7691</v>
       </c>
       <c r="G21" t="n">
         <v>-6.7321</v>
@@ -2092,13 +2092,13 @@
         <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3297</v>
+        <v>-1.1517</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5522</v>
+        <v>-0.4488</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7775</v>
+        <v>-0.703</v>
       </c>
       <c r="V21" t="n">
         <v>0.8995</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-25.5191</v>
+        <v>-24.1402</v>
       </c>
       <c r="E22" t="n">
         <v>-16.2651</v>
       </c>
       <c r="F22" t="n">
-        <v>-9.2539</v>
+        <v>-7.875</v>
       </c>
       <c r="G22" t="n">
         <v>-12.8295</v>
@@ -2170,13 +2170,13 @@
         <v>9.6539</v>
       </c>
       <c r="S22" t="n">
-        <v>-12.9631</v>
+        <v>-11.5842</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4177</v>
+        <v>-0.4178</v>
       </c>
       <c r="U22" t="n">
-        <v>-12.5454</v>
+        <v>-11.1665</v>
       </c>
       <c r="V22" t="n">
         <v>6.0661</v>
